--- a/Two Stage Deterministic equivalent/mean_value.xlsx
+++ b/Two Stage Deterministic equivalent/mean_value.xlsx
@@ -488,34 +488,34 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>2.3213885359649014e8</v>
+        <v>2.3176732139758918e8</v>
       </c>
       <c r="C2">
-        <v>2.5105513840215716e8</v>
+        <v>2.8388793144423115e8</v>
       </c>
       <c r="D2">
-        <v>2.5968331316387916e8</v>
+        <v>2.4366975810651752e8</v>
       </c>
       <c r="E2">
-        <v>3.2379192133903134e8</v>
+        <v>3.881872866558631e8</v>
       </c>
       <c r="F2">
-        <v>2.550589020868702e8</v>
+        <v>3.734124778169728e8</v>
       </c>
       <c r="G2">
-        <v>3.669113581061633e8</v>
+        <v>4.4242701333848864e8</v>
       </c>
       <c r="H2">
-        <v>2.5787895135078928e8</v>
+        <v>4.392435887042854e8</v>
       </c>
       <c r="I2">
-        <v>4.3622484157421625e8</v>
+        <v>3.362413465698265e8</v>
       </c>
       <c r="J2">
-        <v>5.85264441774721e8</v>
+        <v>4.4319645239239764e8</v>
       </c>
       <c r="K2">
-        <v>4.945225225394658e8</v>
+        <v>3.2087965966527903e8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -523,34 +523,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>5.3113998288772416e8</v>
+        <v>3.5865769795493126e8</v>
       </c>
       <c r="C3">
-        <v>4.112549166750792e8</v>
+        <v>5.1192933956713814e8</v>
       </c>
       <c r="D3">
-        <v>3.207117125310195e8</v>
+        <v>7.250251462359896e8</v>
       </c>
       <c r="E3">
-        <v>7.857201250833088e8</v>
+        <v>6.275146117834523e8</v>
       </c>
       <c r="F3">
-        <v>9.655348456750084e8</v>
+        <v>9.716240816030853e8</v>
       </c>
       <c r="G3">
-        <v>5.99253484909089e8</v>
+        <v>7.831324481401613e8</v>
       </c>
       <c r="H3">
-        <v>9.121250990466993e8</v>
+        <v>1.0942627153254974e9</v>
       </c>
       <c r="I3">
-        <v>1.258645944084092e9</v>
+        <v>1.1062879545645196e9</v>
       </c>
       <c r="J3">
-        <v>1.2968148099101803e9</v>
+        <v>6.406265801141999e8</v>
       </c>
       <c r="K3">
-        <v>2.8450872828373396e8</v>
+        <v>1.4936931665415509e9</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -558,34 +558,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>2.9349511810531594e7</v>
+        <v>2.5369590453623164e7</v>
       </c>
       <c r="C4">
-        <v>2.905531264706438e7</v>
+        <v>1.9479190310988065e7</v>
       </c>
       <c r="D4">
-        <v>2.2243290458746906e7</v>
+        <v>2.012660886986489e7</v>
       </c>
       <c r="E4">
-        <v>3.085803134432798e7</v>
+        <v>4.160816913820304e7</v>
       </c>
       <c r="F4">
-        <v>2.0926310854283277e7</v>
+        <v>2.7371105881677136e7</v>
       </c>
       <c r="G4">
-        <v>2.612290390392261e7</v>
+        <v>5.654617606292306e7</v>
       </c>
       <c r="H4">
-        <v>5.227369576443187e7</v>
+        <v>6.308535219306429e7</v>
       </c>
       <c r="I4">
-        <v>5.108285181420374e7</v>
+        <v>7.236958723413187e7</v>
       </c>
       <c r="J4">
-        <v>3.2780946371672317e7</v>
+        <v>5.116836398988973e7</v>
       </c>
       <c r="K4">
-        <v>9.387369111452696e7</v>
+        <v>6.210940239414432e7</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -593,34 +593,34 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>2.8089791544571348e7</v>
+        <v>2.9381733239264697e7</v>
       </c>
       <c r="C5">
-        <v>3.597827114089924e7</v>
+        <v>3.607418017674309e7</v>
       </c>
       <c r="D5">
-        <v>4.103166033603417e7</v>
+        <v>4.2940897631313026e7</v>
       </c>
       <c r="E5">
-        <v>4.8470148955695726e7</v>
+        <v>4.771958497886808e7</v>
       </c>
       <c r="F5">
-        <v>5.562111619910371e7</v>
+        <v>5.2555339964276254e7</v>
       </c>
       <c r="G5">
-        <v>5.9581127183978e7</v>
+        <v>5.945736792804645e7</v>
       </c>
       <c r="H5">
-        <v>6.566586925533773e7</v>
+        <v>6.910608315857941e7</v>
       </c>
       <c r="I5">
-        <v>7.737867533290547e7</v>
+        <v>7.830326519795807e7</v>
       </c>
       <c r="J5">
-        <v>7.399074772524776e7</v>
+        <v>7.902825890165114e7</v>
       </c>
       <c r="K5">
-        <v>8.754042496239477e7</v>
+        <v>7.639048041808045e7</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -628,34 +628,34 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>3.112716110956259e8</v>
+        <v>2.9849544315186626e8</v>
       </c>
       <c r="C6">
-        <v>3.1948422742990446e8</v>
+        <v>3.521101508118506e8</v>
       </c>
       <c r="D6">
-        <v>3.262139252155786e8</v>
+        <v>3.158419687157669e8</v>
       </c>
       <c r="E6">
-        <v>3.7254501761085856e8</v>
+        <v>3.4854733172895265e8</v>
       </c>
       <c r="F6">
-        <v>3.7224875871185553e8</v>
+        <v>3.7163789080892515e8</v>
       </c>
       <c r="G6">
-        <v>3.7954198392649865e8</v>
+        <v>3.598732826802883e8</v>
       </c>
       <c r="H6">
-        <v>3.633476096839813e8</v>
+        <v>3.942683606536381e8</v>
       </c>
       <c r="I6">
-        <v>3.652991721778425e8</v>
+        <v>4.0734089200118583e8</v>
       </c>
       <c r="J6">
-        <v>4.5847014363795435e8</v>
+        <v>4.004061576451051e8</v>
       </c>
       <c r="K6">
-        <v>4.2204770590825653e8</v>
+        <v>3.929078047867905e8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -663,34 +663,34 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>3.478568938419875e8</v>
+        <v>3.6326818409329426e8</v>
       </c>
       <c r="C7">
-        <v>3.151091338174337e8</v>
+        <v>3.334989697242224e8</v>
       </c>
       <c r="D7">
-        <v>3.263212082367508e8</v>
+        <v>3.656852238327569e8</v>
       </c>
       <c r="E7">
-        <v>3.519233978531796e8</v>
+        <v>3.5630804096099585e8</v>
       </c>
       <c r="F7">
-        <v>4.198574775481289e8</v>
+        <v>2.7202035460032415e8</v>
       </c>
       <c r="G7">
-        <v>3.347912095594595e8</v>
+        <v>2.941814066788721e8</v>
       </c>
       <c r="H7">
-        <v>3.760180259873331e8</v>
+        <v>4.1078355471048987e8</v>
       </c>
       <c r="I7">
-        <v>3.244587065845905e8</v>
+        <v>4.396350609154507e8</v>
       </c>
       <c r="J7">
-        <v>3.489211320943955e8</v>
+        <v>3.587796989145897e8</v>
       </c>
       <c r="K7">
-        <v>5.0026484700529045e8</v>
+        <v>3.028785996326894e8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -698,34 +698,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>1.7874282028570822e8</v>
+        <v>1.9496087652704784e8</v>
       </c>
       <c r="C8">
-        <v>2.018244986251431e8</v>
+        <v>1.4722920659098715e8</v>
       </c>
       <c r="D8">
-        <v>2.6183688173688585e8</v>
+        <v>2.9341888442482233e8</v>
       </c>
       <c r="E8">
-        <v>3.9032093893302333e8</v>
+        <v>2.811828208856517e8</v>
       </c>
       <c r="F8">
-        <v>4.127553108824055e8</v>
+        <v>2.462340337460629e8</v>
       </c>
       <c r="G8">
-        <v>4.612456722483132e8</v>
+        <v>4.1641934194742197e8</v>
       </c>
       <c r="H8">
-        <v>2.0782123776455784e8</v>
+        <v>1.0072863426086299e8</v>
       </c>
       <c r="I8">
-        <v>6.730445392582796e8</v>
+        <v>9.144099822924136e8</v>
       </c>
       <c r="J8">
-        <v>5.488237001206683e8</v>
+        <v>8.282962536235878e8</v>
       </c>
       <c r="K8">
-        <v>9.553368047049695e8</v>
+        <v>7.610390064058971e8</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -733,34 +733,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>6.358346932040308e8</v>
+        <v>6.073865627368592e8</v>
       </c>
       <c r="C9">
-        <v>6.700828836970958e8</v>
+        <v>6.888758737229683e8</v>
       </c>
       <c r="D9">
-        <v>7.570479082145071e8</v>
+        <v>7.947521115044473e8</v>
       </c>
       <c r="E9">
-        <v>6.287042621790459e8</v>
+        <v>6.831260864789786e8</v>
       </c>
       <c r="F9">
-        <v>8.349632169048262e8</v>
+        <v>9.163156187640955e8</v>
       </c>
       <c r="G9">
-        <v>7.422197268784173e8</v>
+        <v>8.139923210990083e8</v>
       </c>
       <c r="H9">
-        <v>7.435988528391494e8</v>
+        <v>8.438914494841912e8</v>
       </c>
       <c r="I9">
-        <v>7.307482189051728e8</v>
+        <v>1.0368982335449053e9</v>
       </c>
       <c r="J9">
-        <v>8.986123773174891e8</v>
+        <v>9.709127155833669e8</v>
       </c>
       <c r="K9">
-        <v>9.890884826820745e8</v>
+        <v>1.0830224057637615e9</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -768,34 +768,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>6.642159718210993e8</v>
+        <v>6.502748513231353e8</v>
       </c>
       <c r="C10">
-        <v>6.713865296277735e8</v>
+        <v>7.038145304024808e8</v>
       </c>
       <c r="D10">
-        <v>7.652064160869594e8</v>
+        <v>7.142461535433147e8</v>
       </c>
       <c r="E10">
-        <v>9.125445675237432e8</v>
+        <v>7.724890602993114e8</v>
       </c>
       <c r="F10">
-        <v>1.0234830112221379e9</v>
+        <v>1.0151211967091804e9</v>
       </c>
       <c r="G10">
-        <v>8.158860893453147e8</v>
+        <v>1.1600784418514504e9</v>
       </c>
       <c r="H10">
-        <v>1.1502371628901677e9</v>
+        <v>1.0513777414535644e9</v>
       </c>
       <c r="I10">
-        <v>1.428073259298306e9</v>
+        <v>1.0929386361921482e9</v>
       </c>
       <c r="J10">
-        <v>1.9707865050575142e9</v>
+        <v>2.6637748519777136e9</v>
       </c>
       <c r="K10">
-        <v>2.8540647567479105e9</v>
+        <v>1.9707828617937682e9</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -803,34 +803,34 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>4.066740208347319e8</v>
+        <v>4.391542962772902e8</v>
       </c>
       <c r="C11">
-        <v>4.256312492144178e8</v>
+        <v>3.2834881497732985e8</v>
       </c>
       <c r="D11">
-        <v>3.5757020795404243e8</v>
+        <v>4.690185061503682e8</v>
       </c>
       <c r="E11">
-        <v>4.421908574351816e8</v>
+        <v>2.924823285109452e8</v>
       </c>
       <c r="F11">
-        <v>2.904385229712253e8</v>
+        <v>4.324996903071235e8</v>
       </c>
       <c r="G11">
-        <v>4.037950119346902e8</v>
+        <v>3.520349898596481e8</v>
       </c>
       <c r="H11">
-        <v>5.519657635226264e8</v>
+        <v>5.0498163568186605e8</v>
       </c>
       <c r="I11">
-        <v>2.933067040885344e8</v>
+        <v>5.122841932386581e8</v>
       </c>
       <c r="J11">
-        <v>6.343074829301624e8</v>
+        <v>5.183449882596009e8</v>
       </c>
       <c r="K11">
-        <v>2.4714461454889435e8</v>
+        <v>4.650371088306482e8</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -838,34 +838,34 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>6.108228550852809e8</v>
+        <v>6.367787284700239e8</v>
       </c>
       <c r="C12">
-        <v>6.365102885002342e8</v>
+        <v>6.046095082239668e8</v>
       </c>
       <c r="D12">
-        <v>6.953400757673562e8</v>
+        <v>6.773482621507664e8</v>
       </c>
       <c r="E12">
-        <v>6.771970025403376e8</v>
+        <v>7.395920536367661e8</v>
       </c>
       <c r="F12">
-        <v>6.603938793737653e8</v>
+        <v>6.355541180198092e8</v>
       </c>
       <c r="G12">
-        <v>5.3301404875443286e8</v>
+        <v>6.342618698347428e8</v>
       </c>
       <c r="H12">
-        <v>7.39639473749515e8</v>
+        <v>8.013973518627787e8</v>
       </c>
       <c r="I12">
-        <v>5.50663467345458e8</v>
+        <v>7.373725081136311e8</v>
       </c>
       <c r="J12">
-        <v>6.074664661734176e8</v>
+        <v>7.288378713553638e8</v>
       </c>
       <c r="K12">
-        <v>8.412888913598237e8</v>
+        <v>7.083257606615317e8</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -873,34 +873,34 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>5.0268187089457214e8</v>
+        <v>3.5490901409539425e8</v>
       </c>
       <c r="C13">
-        <v>3.156746616903976e8</v>
+        <v>4.5276540059838927e8</v>
       </c>
       <c r="D13">
-        <v>3.6089345409533626e8</v>
+        <v>5.390205911126268e8</v>
       </c>
       <c r="E13">
-        <v>2.987296497372293e8</v>
+        <v>5.629316291621084e8</v>
       </c>
       <c r="F13">
-        <v>2.9704073932196707e8</v>
+        <v>3.3789268288146126e8</v>
       </c>
       <c r="G13">
-        <v>6.149904757310698e8</v>
+        <v>7.072888257087879e8</v>
       </c>
       <c r="H13">
-        <v>5.190805072496564e8</v>
+        <v>4.1521873240159595e8</v>
       </c>
       <c r="I13">
-        <v>5.881524019721736e8</v>
+        <v>4.7533962318375826e8</v>
       </c>
       <c r="J13">
-        <v>6.269455800163603e8</v>
+        <v>9.547379651207238e8</v>
       </c>
       <c r="K13">
-        <v>5.467539636725239e8</v>
+        <v>1.0282984090815811e9</v>
       </c>
     </row>
   </sheetData>
